--- a/12-06-26/mubeen.xlsx
+++ b/12-06-26/mubeen.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FA0569E-3B55-4E55-A4CC-CE2E6DEE21C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F222567E-CA79-4FF5-8221-B8931EDE215F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1581" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="124">
   <si>
     <t>Gm</t>
   </si>
@@ -413,6 +413,9 @@
   </si>
   <si>
     <t>Customer Name : Bravo Store</t>
+  </si>
+  <si>
+    <t>4031762-5</t>
   </si>
 </sst>
 </file>
@@ -4996,39 +4999,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="114"/>
-      <c r="H17" s="115">
-        <v>24</v>
-      </c>
+      <c r="H17" s="115"/>
       <c r="I17" s="116">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
-        <v>1259.0999999999999</v>
-      </c>
-      <c r="J17" s="117">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J17" s="117"/>
       <c r="K17" s="1">
         <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
         <f t="shared" ref="L17:L21" si="4">I17*8%</f>
-        <v>100.72799999999999</v>
+        <v>0</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>1158.3719999999998</v>
+        <v>0</v>
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>266.38358999999997</v>
+        <v>0</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>7.1237779499999991</v>
+        <v>0</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>1431.8793679499997</v>
+        <v>0</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -5116,39 +5115,35 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="114"/>
-      <c r="H19" s="115">
-        <v>24</v>
-      </c>
+      <c r="H19" s="115"/>
       <c r="I19" s="116">
         <f t="shared" si="2"/>
-        <v>1743.3600000000001</v>
-      </c>
-      <c r="J19" s="117">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J19" s="117"/>
       <c r="K19" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
-        <v>139.46880000000002</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>1603.8912</v>
+        <v>0</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>368.83686399999999</v>
+        <v>0</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>9.86364032</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>1982.59170432</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5446,11 +5441,11 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>3002.46</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
@@ -5459,23 +5454,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>240.1968</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>2762.2631999999999</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>635.22045400000002</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>16.987418269999999</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>3414.4710722699997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -5525,7 +5520,7 @@
       <c r="O28" s="222"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>3002.46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5546,7 +5541,7 @@
       <c r="O29" s="224"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>240.1968</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5589,7 +5584,7 @@
       <c r="O31" s="224"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>2762.2631999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5614,7 +5609,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>635.22045400000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -5636,7 +5631,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>3397.4836539999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5661,7 +5656,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>16.987418269999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -5671,7 +5666,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>3414.4710722699997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -23454,7 +23449,7 @@
       </c>
       <c r="U14" s="164">
         <f>+'1'!P35</f>
-        <v>1702.7365662000002</v>
+        <v>0</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -23507,7 +23502,7 @@
       </c>
       <c r="U15" s="164">
         <f>+'2'!P35</f>
-        <v>3099.3405109999999</v>
+        <v>0</v>
       </c>
       <c r="XFD15" t="s">
         <v>81</v>
@@ -23540,11 +23535,11 @@
       <c r="G16" s="114"/>
       <c r="H16" s="172">
         <f>+'1'!H16+'2'!H16+'4'!H16+'3'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16</f>
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="I16" s="1">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>1573.875</v>
+        <v>786.9375</v>
       </c>
       <c r="J16" s="172">
         <f>+'1'!J16+'2'!J16+'4'!J16+'3'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16</f>
@@ -23556,23 +23551,23 @@
       </c>
       <c r="L16" s="175">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>125.91</v>
+        <v>62.954999999999998</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>1447.9649999999999</v>
+        <v>723.98249999999996</v>
       </c>
       <c r="N16" s="101">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>318.5523</v>
+        <v>159.27615</v>
       </c>
       <c r="O16" s="101">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>26.497759500000001</v>
+        <v>4.4162932499999998</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>1793.0150595</v>
+        <v>887.67494324999996</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="T16" s="163" t="str">
@@ -23614,15 +23609,15 @@
       <c r="G17" s="114"/>
       <c r="H17" s="172">
         <f>+'1'!H17+'2'!H17+'4'!H17+'3'!H17+'5'!H17+'6'!H17+'7'!H17+'8'!H17+'9'!H17+'10'!H17+'11'!H17+'12'!H17+'13'!H17+'14'!H17+'15'!H17+'16'!H17</f>
-        <v>64</v>
+        <v>30</v>
       </c>
       <c r="I17" s="1">
         <f t="shared" ref="I17:I23" si="1">(G17*D17)*F17+H17*F17</f>
-        <v>3357.6</v>
+        <v>1573.875</v>
       </c>
       <c r="J17" s="172">
         <f>+'1'!J17+'2'!J17+'4'!J17+'3'!J17+'5'!J17+'6'!J17+'7'!J17+'8'!J17+'9'!J17+'10'!J17+'11'!J17+'12'!J17</f>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K17" s="172">
         <f>+'1'!K17+'2'!K17+'4'!K17+'3'!K17+'5'!K17+'6'!K17+'7'!K17+'8'!K17+'9'!K17+'10'!K17</f>
@@ -23630,23 +23625,23 @@
       </c>
       <c r="L17" s="175">
         <f>+'1'!L17+'2'!L17+'4'!L17+'3'!L17+'5'!L17+'6'!L17+'7'!L17+'8'!L17+'9'!L17+'10'!L17</f>
-        <v>268.608</v>
+        <v>167.88</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="2">I17-K17-L17</f>
-        <v>3088.9919999999997</v>
+        <v>1405.9949999999999</v>
       </c>
       <c r="N17" s="101">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>748.82873999999993</v>
+        <v>304.91205000000002</v>
       </c>
       <c r="O17" s="101">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>55.2119547</v>
+        <v>8.5545352500000007</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="0"/>
-        <v>3893.0326946999999</v>
+        <v>1719.4615852499999</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="163" t="str">
@@ -23655,7 +23650,7 @@
       </c>
       <c r="U17" s="164">
         <f>+'3'!P35</f>
-        <v>5813.4381135000003</v>
+        <v>5267.5008117000007</v>
       </c>
       <c r="XFD17" t="s">
         <v>83</v>
@@ -23688,11 +23683,11 @@
       <c r="G18" s="114"/>
       <c r="H18" s="172">
         <f>+'1'!H18+'2'!H18+'4'!H18+'3'!H18+'5'!H18+'6'!H18+'7'!H18+'8'!H18+'9'!H18+'10'!H18+'11'!H18+'12'!H18+'13'!H18+'14'!H18+'15'!H18+'16'!H18</f>
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="I18" s="1">
         <f t="shared" si="1"/>
-        <v>2623.125</v>
+        <v>1836.1875</v>
       </c>
       <c r="J18" s="172">
         <f>+'1'!J18+'2'!J18+'4'!J18+'3'!J18+'5'!J18+'6'!J18+'7'!J18+'8'!J18+'9'!J18+'10'!J18+'11'!J18+'12'!J18</f>
@@ -23704,23 +23699,23 @@
       </c>
       <c r="L18" s="175">
         <f>+'1'!L18+'2'!L18+'4'!L18+'3'!L18+'5'!L18+'6'!L18+'7'!L18+'8'!L18+'9'!L18+'10'!L18</f>
-        <v>209.84999999999997</v>
+        <v>188.86500000000001</v>
       </c>
       <c r="M18" s="118">
         <f t="shared" si="2"/>
-        <v>2413.2750000000001</v>
+        <v>1647.3225</v>
       </c>
       <c r="N18" s="101">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>542.46225000000004</v>
+        <v>334.92060000000004</v>
       </c>
       <c r="O18" s="101">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>56.228258249999996</v>
+        <v>9.9112155000000008</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="0"/>
-        <v>3011.9655082500003</v>
+        <v>1992.1543155000002</v>
       </c>
       <c r="T18" s="163" t="str">
         <f>+'5'!A5</f>
@@ -23758,15 +23753,15 @@
       <c r="G19" s="114"/>
       <c r="H19" s="172">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19</f>
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>7699.84</v>
+        <v>5084.8</v>
       </c>
       <c r="J19" s="172">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K19" s="172">
         <f>+'1'!K19+'2'!K19+'4'!K19+'3'!K19+'5'!K19+'6'!K19+'7'!K19+'8'!K19+'9'!K19+'10'!K19</f>
@@ -23774,23 +23769,23 @@
       </c>
       <c r="L19" s="175">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>615.98720000000003</v>
+        <v>406.78399999999999</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="2"/>
-        <v>7083.8528000000006</v>
+        <v>4678.0160000000005</v>
       </c>
       <c r="N19" s="101">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>1622.3708159999996</v>
+        <v>1061.1251199999999</v>
       </c>
       <c r="O19" s="101">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>87.877547520000007</v>
+        <v>53.155046400000003</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="0"/>
-        <v>8794.1011635199993</v>
+        <v>5792.2961664000004</v>
       </c>
       <c r="T19" s="163" t="str">
         <f>+'6'!A5</f>
@@ -23798,7 +23793,7 @@
       </c>
       <c r="U19" s="164">
         <f>+'6'!P35</f>
-        <v>2437.9008974999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23844,23 +23839,23 @@
       </c>
       <c r="L20" s="175">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>464.89600000000002</v>
+        <v>523.00800000000004</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="2"/>
-        <v>5346.3040000000001</v>
+        <v>5288.192</v>
       </c>
       <c r="N20" s="101">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>1288.0524799999998</v>
+        <v>1221.2236800000001</v>
       </c>
       <c r="O20" s="101">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>83.049312000000015</v>
+        <v>49.492537599999999</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="0"/>
-        <v>6717.4057920000005</v>
+        <v>6558.9082176000002</v>
       </c>
       <c r="T20" s="163" t="str">
         <f>+'7'!A5</f>
@@ -23898,11 +23893,11 @@
       <c r="G21" s="114"/>
       <c r="H21" s="172">
         <f>+'1'!H21+'2'!H21+'4'!H21+'3'!H21+'5'!H21+'6'!H21+'7'!H21+'8'!H21+'9'!H21+'10'!H21+'11'!H21+'12'!H21+'13'!H21+'14'!H21+'15'!H21+'16'!H21</f>
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="I21" s="1">
         <f t="shared" si="1"/>
-        <v>7409.28</v>
+        <v>6537.6</v>
       </c>
       <c r="J21" s="172">
         <f>+'1'!J21+'2'!J21+'4'!J21+'3'!J21+'5'!J21+'6'!J21+'7'!J21+'8'!J21+'9'!J21+'10'!J21+'11'!J21+'12'!J21</f>
@@ -23914,23 +23909,23 @@
       </c>
       <c r="L21" s="175">
         <f>+'1'!L21+'2'!L21+'4'!L21+'3'!L21+'5'!L21+'6'!L21+'7'!L21+'8'!L21+'9'!L21+'10'!L21</f>
-        <v>592.74239999999998</v>
+        <v>581.12</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="2"/>
-        <v>6816.5375999999997</v>
+        <v>5956.4800000000005</v>
       </c>
       <c r="N21" s="101">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>1547.580672</v>
+        <v>1304.32384</v>
       </c>
       <c r="O21" s="101">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>118.77947520000001</v>
+        <v>60.763359999999999</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="0"/>
-        <v>8482.8977472000006</v>
+        <v>7321.5672000000004</v>
       </c>
       <c r="T21" s="163" t="str">
         <f>+'8'!A5</f>
@@ -23938,7 +23933,7 @@
       </c>
       <c r="U21" s="164">
         <f>+'8'!P35</f>
-        <v>3414.4710722699997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23968,11 +23963,11 @@
       <c r="G22" s="114"/>
       <c r="H22" s="172">
         <f>+'1'!H22+'2'!H22+'4'!H22+'3'!H22+'5'!H22+'6'!H22+'7'!H22+'8'!H22+'9'!H22+'10'!H22+'11'!H22+'12'!H22+'13'!H22+'14'!H22+'15'!H22+'16'!H22</f>
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="I22" s="1">
         <f t="shared" si="1"/>
-        <v>2510.7200000000003</v>
+        <v>0</v>
       </c>
       <c r="J22" s="172">
         <f>+'1'!J22+'2'!J22+'4'!J22+'3'!J22+'5'!J22+'6'!J22+'7'!J22+'8'!J22+'9'!J22+'10'!J22+'11'!J22+'12'!J22</f>
@@ -23980,27 +23975,27 @@
       </c>
       <c r="K22" s="172">
         <f>+'1'!K22+'2'!K22+'4'!K22+'3'!K22+'5'!K22+'6'!K22+'7'!K22+'8'!K22+'9'!K22+'10'!K22</f>
-        <v>87.875200000000021</v>
+        <v>0</v>
       </c>
       <c r="L22" s="175">
         <f>+'1'!L22+'2'!L22+'4'!L22+'3'!L22+'5'!L22+'6'!L22+'7'!L22+'8'!L22+'9'!L22+'10'!L22</f>
-        <v>125.53600000000003</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="2"/>
-        <v>2297.3088000000002</v>
+        <v>0</v>
       </c>
       <c r="N22" s="101">
         <f>+'1'!N22+'2'!N22+'4'!N22+'3'!N22+'5'!N22+'6'!N22+'7'!N22+'8'!N22+'9'!N22+'10'!N22</f>
-        <v>447.97521600000005</v>
+        <v>0</v>
       </c>
       <c r="O22" s="101">
         <f>+'1'!O22+'2'!O22+'4'!O22+'3'!O22+'5'!O22+'6'!O22+'7'!O22+'8'!O22+'9'!O22+'10'!O22</f>
-        <v>34.746795600000006</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="0"/>
-        <v>2780.0308116000006</v>
+        <v>0</v>
       </c>
       <c r="T22" s="163" t="str">
         <f>+'9'!A5</f>
@@ -24158,7 +24153,7 @@
       <c r="B25" s="210"/>
       <c r="C25" s="211">
         <f>H25/40</f>
-        <v>12.4</v>
+        <v>8</v>
       </c>
       <c r="D25" s="205"/>
       <c r="E25" s="205"/>
@@ -24169,39 +24164,39 @@
       </c>
       <c r="H25" s="177">
         <f t="shared" si="3"/>
-        <v>496</v>
+        <v>320</v>
       </c>
       <c r="I25" s="178">
         <f t="shared" si="3"/>
-        <v>30985.64</v>
+        <v>21630.6</v>
       </c>
       <c r="J25" s="177">
         <f t="shared" si="3"/>
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K25" s="178">
         <f t="shared" si="3"/>
-        <v>87.875200000000021</v>
+        <v>0</v>
       </c>
       <c r="L25" s="179">
         <f t="shared" si="3"/>
-        <v>2403.5295999999998</v>
+        <v>1930.6120000000001</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="3"/>
-        <v>28494.235199999999</v>
+        <v>19699.988000000001</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>6515.8224739999996</v>
+        <v>4385.7814400000007</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>462.39110277000003</v>
+        <v>186.29298800000001</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>35472.448776770005</v>
+        <v>24272.062428000001</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24331,7 +24326,7 @@
       </c>
       <c r="U30" s="165">
         <f>SUM(U14:U28)</f>
-        <v>35472.448776769997</v>
+        <v>24272.062427999997</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24364,7 +24359,7 @@
       <c r="O32" s="222"/>
       <c r="P32" s="152">
         <f>I25</f>
-        <v>30985.64</v>
+        <v>21630.6</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24385,7 +24380,7 @@
       <c r="O33" s="224"/>
       <c r="P33" s="153">
         <f>L25</f>
-        <v>2403.5295999999998</v>
+        <v>1930.6120000000001</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24406,7 +24401,7 @@
       <c r="O34" s="224"/>
       <c r="P34" s="154">
         <f>K25</f>
-        <v>87.875200000000021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24428,7 +24423,7 @@
       <c r="O35" s="224"/>
       <c r="P35" s="153">
         <f>P32-P33-P34</f>
-        <v>28494.235199999999</v>
+        <v>19699.987999999998</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24453,7 +24448,7 @@
       </c>
       <c r="P36" s="153">
         <f>N25</f>
-        <v>6515.8224739999996</v>
+        <v>4385.7814400000007</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24475,7 +24470,7 @@
       <c r="O37" s="226"/>
       <c r="P37" s="153">
         <f>P35+P36</f>
-        <v>35010.057673999996</v>
+        <v>24085.769439999996</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24500,7 +24495,7 @@
       </c>
       <c r="P38" s="153">
         <f>O38*P37</f>
-        <v>875.25144184999999</v>
+        <v>602.14423599999998</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24510,7 +24505,7 @@
       <c r="O39" s="204"/>
       <c r="P39" s="160">
         <f>P37+P38</f>
-        <v>35885.309115849996</v>
+        <v>24687.913675999996</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -25348,37 +25343,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>40</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="3"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="6"/>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>258.44724000000002</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="1"/>
-        <v>8.4713262000000018</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="2"/>
-        <v>1702.7365662000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25508,36 +25501,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>258.44724000000002</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>8.4713262000000018</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>1702.7365662000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25587,7 +25580,7 @@
       <c r="O28" s="222"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>1569.2000000000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25608,7 +25601,7 @@
       <c r="O29" s="224"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>78.460000000000022</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25629,7 +25622,7 @@
       <c r="O30" s="224"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>54.922000000000011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25651,7 +25644,7 @@
       <c r="O31" s="224"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1435.8180000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25676,7 +25669,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>258.44724000000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -25698,7 +25691,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>1694.2652400000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25723,7 +25716,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>8.4713262000000018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -25733,7 +25726,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>1702.7365662000002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -26403,39 +26396,35 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="114"/>
-      <c r="H19" s="115">
-        <v>12</v>
-      </c>
+      <c r="H19" s="115"/>
       <c r="I19" s="116">
         <f t="shared" si="2"/>
-        <v>871.68000000000006</v>
-      </c>
-      <c r="J19" s="117">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J19" s="117"/>
       <c r="K19" s="1">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L19" s="105">
         <f t="shared" si="4"/>
-        <v>69.734400000000008</v>
+        <v>0</v>
       </c>
       <c r="M19" s="118">
         <f t="shared" si="5"/>
-        <v>801.94560000000001</v>
+        <v>0</v>
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>192.40883199999999</v>
+        <v>0</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>24.858860800000002</v>
+        <v>0</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>1019.2132928</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26519,12 +26508,10 @@
         <v>72.64</v>
       </c>
       <c r="G21" s="114"/>
-      <c r="H21" s="115">
-        <v>12</v>
-      </c>
+      <c r="H21" s="115"/>
       <c r="I21" s="116">
         <f t="shared" si="2"/>
-        <v>871.68000000000006</v>
+        <v>0</v>
       </c>
       <c r="J21" s="117"/>
       <c r="K21" s="1">
@@ -26533,23 +26520,23 @@
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
-        <v>69.734400000000008</v>
+        <v>0</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>801.94560000000001</v>
+        <v>0</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>176.428032</v>
+        <v>0</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>24.459340800000003</v>
+        <v>0</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>1002.8329728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26577,37 +26564,35 @@
         <v>39.230000000000004</v>
       </c>
       <c r="G22" s="114"/>
-      <c r="H22" s="115">
-        <v>24</v>
-      </c>
+      <c r="H22" s="115"/>
       <c r="I22" s="116">
         <f t="shared" si="2"/>
-        <v>941.5200000000001</v>
+        <v>0</v>
       </c>
       <c r="J22" s="117"/>
       <c r="K22" s="1">
         <f>I22*3.5%</f>
-        <v>32.95320000000001</v>
+        <v>0</v>
       </c>
       <c r="L22" s="120">
         <f>I22*5%</f>
-        <v>47.076000000000008</v>
+        <v>0</v>
       </c>
       <c r="M22" s="118">
         <f t="shared" si="5"/>
-        <v>861.49080000000004</v>
+        <v>0</v>
       </c>
       <c r="N22" s="118">
         <f t="shared" si="0"/>
-        <v>189.527976</v>
+        <v>0</v>
       </c>
       <c r="O22" s="119">
         <f t="shared" si="6"/>
-        <v>26.275469400000006</v>
+        <v>0</v>
       </c>
       <c r="P22" s="120">
         <f t="shared" si="1"/>
-        <v>1077.2942454000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26737,36 +26722,36 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>2684.88</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
         <f t="shared" si="9"/>
-        <v>32.95320000000001</v>
+        <v>0</v>
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>186.54480000000001</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>2465.3820000000001</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>558.36483999999996</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>75.593671000000015</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>3099.3405110000003</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -26816,7 +26801,7 @@
       <c r="O28" s="222"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>2684.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26837,7 +26822,7 @@
       <c r="O29" s="224"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>186.54480000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26858,7 +26843,7 @@
       <c r="O30" s="224"/>
       <c r="P30" s="154">
         <f>K25</f>
-        <v>32.95320000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26880,7 +26865,7 @@
       <c r="O31" s="224"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>2465.3820000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26905,7 +26890,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>558.36483999999996</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26927,7 +26912,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>3023.7468399999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26952,7 +26937,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>75.593671000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26962,7 +26947,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>3099.3405109999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -27254,8 +27239,8 @@
       <c r="A10" s="227" t="s">
         <v>95</v>
       </c>
-      <c r="B10" s="169">
-        <v>0</v>
+      <c r="B10" s="169" t="s">
+        <v>123</v>
       </c>
       <c r="C10" s="75"/>
       <c r="F10" s="70"/>
@@ -27279,11 +27264,11 @@
     <row r="11" spans="1:19 16383:16384" x14ac:dyDescent="0.35">
       <c r="A11" s="227"/>
       <c r="B11" s="76" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C11" s="77" t="str">
         <f>IF($O34&gt;2.49%,"No","Yes")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
@@ -27305,11 +27290,11 @@
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="77" t="str">
         <f>IF($O32&gt;21.99%,"No","Yes")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
@@ -27330,7 +27315,7 @@
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="228"/>
       <c r="B13" s="56">
-        <v>0</v>
+        <v>300403176219</v>
       </c>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -27418,11 +27403,11 @@
       <c r="M15" s="250"/>
       <c r="N15" s="92">
         <f>IF(B12="Registered",18%,22%)</f>
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="O15" s="93">
         <f>IF(B11="Filer",0.5%,2.5%)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P15" s="94" t="s">
         <v>1</v>
@@ -27467,7 +27452,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="105">
-        <f>I16*8%</f>
+        <f>I16*12%</f>
         <v>0</v>
       </c>
       <c r="M16" s="106">
@@ -27531,24 +27516,24 @@
         <v>0</v>
       </c>
       <c r="L17" s="105">
-        <f t="shared" ref="L17:L21" si="4">I17*8%</f>
-        <v>83.94</v>
+        <f t="shared" ref="L17:L21" si="4">I17*12%</f>
+        <v>125.91</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>965.31</v>
+        <v>923.34</v>
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>223.90995000000001</v>
+        <v>175.64445000000001</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>29.730498749999999</v>
+        <v>5.4949222500000001</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>1218.9504487499999</v>
+        <v>1104.4793722499999</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -27596,23 +27581,23 @@
       </c>
       <c r="L18" s="105">
         <f t="shared" si="4"/>
-        <v>83.94</v>
+        <v>125.91</v>
       </c>
       <c r="M18" s="118">
         <f t="shared" si="5"/>
-        <v>965.31</v>
+        <v>923.34</v>
       </c>
       <c r="N18" s="118">
         <f t="shared" si="0"/>
-        <v>223.90995000000001</v>
+        <v>175.64445000000001</v>
       </c>
       <c r="O18" s="119">
         <f t="shared" si="6"/>
-        <v>29.730498749999999</v>
+        <v>5.4949222500000001</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="1"/>
-        <v>1218.9504487499999</v>
+        <v>1104.4793722499999</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27712,23 +27697,23 @@
       </c>
       <c r="L20" s="105">
         <f t="shared" si="4"/>
-        <v>116.224</v>
+        <v>174.33599999999998</v>
       </c>
       <c r="M20" s="118">
         <f t="shared" si="5"/>
-        <v>1336.576</v>
+        <v>1278.4639999999999</v>
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>310.02751999999998</v>
+        <v>243.19871999999998</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>41.165088000000004</v>
+        <v>7.6083135999999989</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>1687.7686080000001</v>
+        <v>1529.2710335999998</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27772,23 +27757,23 @@
       </c>
       <c r="L21" s="105">
         <f t="shared" si="4"/>
-        <v>116.224</v>
+        <v>174.33599999999998</v>
       </c>
       <c r="M21" s="118">
         <f t="shared" si="5"/>
-        <v>1336.576</v>
+        <v>1278.4639999999999</v>
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>310.02751999999998</v>
+        <v>243.19871999999998</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>41.165088000000004</v>
+        <v>7.6083135999999989</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>1687.7686080000001</v>
+        <v>1529.2710335999998</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -27987,23 +27972,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>400.32799999999997</v>
+        <v>600.49199999999996</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>4603.7719999999999</v>
+        <v>4403.6080000000002</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>1067.8749400000002</v>
+        <v>837.68633999999997</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>141.79117350000001</v>
+        <v>26.206471699999998</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>5813.4381135000003</v>
+        <v>5267.5008116999998</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -28074,7 +28059,7 @@
       <c r="O29" s="224"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>400.32799999999997</v>
+        <v>600.49199999999996</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28117,7 +28102,7 @@
       <c r="O31" s="224"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>4603.7720000000008</v>
+        <v>4403.6080000000002</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28138,11 +28123,11 @@
       </c>
       <c r="O32" s="156">
         <f>IF(B12="Registered",18%,22%)</f>
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>1067.8749400000002</v>
+        <v>837.68633999999997</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -28164,7 +28149,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>5671.6469400000005</v>
+        <v>5241.2943400000004</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28185,11 +28170,11 @@
       </c>
       <c r="O34" s="159">
         <f>IF(B11="Filer",0.5%,2.5%)</f>
-        <v>2.5000000000000001E-2</v>
+        <v>5.0000000000000001E-3</v>
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>141.79117350000001</v>
+        <v>26.206471700000002</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -28199,7 +28184,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>5813.4381135000003</v>
+        <v>5267.5008117000007</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -31158,12 +31143,10 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="100"/>
-      <c r="H16" s="101">
-        <v>15</v>
-      </c>
+      <c r="H16" s="101"/>
       <c r="I16" s="102">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>786.9375</v>
+        <v>0</v>
       </c>
       <c r="J16" s="103"/>
       <c r="K16" s="104">
@@ -31172,23 +31155,23 @@
       </c>
       <c r="L16" s="105">
         <f>I16*8%</f>
-        <v>62.954999999999998</v>
+        <v>0</v>
       </c>
       <c r="M16" s="106">
         <f>I16-K16-L16</f>
-        <v>723.98249999999996</v>
+        <v>0</v>
       </c>
       <c r="N16" s="106">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>159.27615</v>
+        <v>0</v>
       </c>
       <c r="O16" s="107">
         <f>(N16+M16)*$O$15</f>
-        <v>22.081466250000002</v>
+        <v>0</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>905.34011624999994</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="XFD16" t="s">
@@ -31220,39 +31203,35 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G17" s="114"/>
-      <c r="H17" s="115">
-        <v>10</v>
-      </c>
+      <c r="H17" s="115"/>
       <c r="I17" s="116">
         <f t="shared" ref="I17:I23" si="2">(G17*D17)*F17+H17*F17</f>
-        <v>524.625</v>
-      </c>
-      <c r="J17" s="117">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="J17" s="117"/>
       <c r="K17" s="1">
         <f t="shared" ref="K17:K21" si="3">I17*$K$13</f>
         <v>0</v>
       </c>
       <c r="L17" s="105">
         <f t="shared" ref="L17:L21" si="4">I17*8%</f>
-        <v>41.97</v>
+        <v>0</v>
       </c>
       <c r="M17" s="118">
         <f t="shared" ref="M17:M23" si="5">I17-K17-L17</f>
-        <v>482.65499999999997</v>
+        <v>0</v>
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>129.26760000000002</v>
+        <v>0</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>15.298065000000001</v>
+        <v>0</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>627.22066499999994</v>
+        <v>0</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -31284,12 +31263,10 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G18" s="114"/>
-      <c r="H18" s="115">
-        <v>15</v>
-      </c>
+      <c r="H18" s="115"/>
       <c r="I18" s="116">
         <f t="shared" si="2"/>
-        <v>786.9375</v>
+        <v>0</v>
       </c>
       <c r="J18" s="117"/>
       <c r="K18" s="1">
@@ -31298,23 +31275,23 @@
       </c>
       <c r="L18" s="105">
         <f t="shared" si="4"/>
-        <v>62.954999999999998</v>
+        <v>0</v>
       </c>
       <c r="M18" s="118">
         <f t="shared" si="5"/>
-        <v>723.98249999999996</v>
+        <v>0</v>
       </c>
       <c r="N18" s="118">
         <f t="shared" si="0"/>
-        <v>159.27615</v>
+        <v>0</v>
       </c>
       <c r="O18" s="119">
         <f t="shared" si="6"/>
-        <v>22.081466250000002</v>
+        <v>0</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="1"/>
-        <v>905.34011624999994</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31668,11 +31645,11 @@
       </c>
       <c r="H25" s="136">
         <f t="shared" si="9"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I25" s="137">
         <f t="shared" si="9"/>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
       <c r="J25" s="138"/>
       <c r="K25" s="139">
@@ -31681,23 +31658,23 @@
       </c>
       <c r="L25" s="140">
         <f t="shared" si="9"/>
-        <v>167.88</v>
+        <v>0</v>
       </c>
       <c r="M25" s="141">
         <f t="shared" si="9"/>
-        <v>1930.62</v>
+        <v>0</v>
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>447.81990000000008</v>
+        <v>0</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>59.460997500000005</v>
+        <v>0</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>2437.9008974999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -31747,7 +31724,7 @@
       <c r="O28" s="222"/>
       <c r="P28" s="152">
         <f>I25</f>
-        <v>2098.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31768,7 +31745,7 @@
       <c r="O29" s="224"/>
       <c r="P29" s="153">
         <f>L25</f>
-        <v>167.88</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31811,7 +31788,7 @@
       <c r="O31" s="224"/>
       <c r="P31" s="153">
         <f>P28-P29-P30</f>
-        <v>1930.62</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31836,7 +31813,7 @@
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>447.81990000000008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -31858,7 +31835,7 @@
       <c r="O33" s="226"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>2378.4398999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -31883,7 +31860,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>59.460997499999998</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -31893,7 +31870,7 @@
       <c r="O35" s="204"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>2437.9008974999997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">

--- a/12-06-26/mubeen.xlsx
+++ b/12-06-26/mubeen.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B62CA3-13ED-44BB-9347-BB95849633F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78B0E526-D576-494D-A7A1-A1073A6B1E87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="125">
   <si>
     <t>Gm</t>
   </si>
@@ -416,6 +416,9 @@
   </si>
   <si>
     <t>4031762-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
   </si>
 </sst>
 </file>
@@ -3384,7 +3387,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -3412,7 +3415,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -4617,7 +4620,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -4645,7 +4648,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -5838,7 +5841,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -5866,7 +5869,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -7059,7 +7062,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -7087,7 +7090,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -8280,7 +8283,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -8308,7 +8311,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -9501,7 +9504,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -9529,7 +9532,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -10719,7 +10722,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -10747,7 +10750,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -11936,7 +11939,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -11964,7 +11967,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -13153,7 +13156,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -13181,7 +13184,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -14370,7 +14373,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -14398,7 +14401,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -18337,7 +18340,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -18365,7 +18368,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -19554,7 +19557,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -19582,7 +19585,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -20771,7 +20774,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -20799,7 +20802,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -21988,7 +21991,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -22016,7 +22019,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23210,7 +23213,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -23238,7 +23241,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -23559,15 +23562,15 @@
       </c>
       <c r="N16" s="101">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>159.27615</v>
+        <v>130.31684999999999</v>
       </c>
       <c r="O16" s="101">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>4.4162932499999998</v>
+        <v>4.2714967499999998</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>887.67494324999996</v>
+        <v>858.57084674999999</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="T16" s="163" t="str">
@@ -23633,15 +23636,15 @@
       </c>
       <c r="N17" s="101">
         <f>+'1'!N17+'2'!N17+'4'!N17+'3'!N17+'5'!N17+'6'!N17+'7'!N17+'8'!N17+'9'!N17+'10'!N17</f>
-        <v>304.91205000000002</v>
+        <v>281.40885000000003</v>
       </c>
       <c r="O17" s="101">
         <f>+'1'!O17+'2'!O17+'4'!O17+'3'!O17+'5'!O17+'6'!O17+'7'!O17+'8'!O17+'9'!O17+'10'!O17</f>
-        <v>8.5545352500000007</v>
+        <v>8.4370192500000005</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="0"/>
-        <v>1719.4615852499999</v>
+        <v>1695.84086925</v>
       </c>
       <c r="S17" s="64"/>
       <c r="T17" s="163" t="str">
@@ -23707,15 +23710,15 @@
       </c>
       <c r="N18" s="101">
         <f>+'1'!N18+'2'!N18+'4'!N18+'3'!N18+'5'!N18+'6'!N18+'7'!N18+'8'!N18+'9'!N18+'10'!N18</f>
-        <v>334.92060000000004</v>
+        <v>305.96129999999999</v>
       </c>
       <c r="O18" s="101">
         <f>+'1'!O18+'2'!O18+'4'!O18+'3'!O18+'5'!O18+'6'!O18+'7'!O18+'8'!O18+'9'!O18+'10'!O18</f>
-        <v>9.9112155000000008</v>
+        <v>9.7664189999999991</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="0"/>
-        <v>1992.1543155000002</v>
+        <v>1963.050219</v>
       </c>
       <c r="T18" s="163" t="str">
         <f>+'5'!A5</f>
@@ -23723,7 +23726,7 @@
       </c>
       <c r="U18" s="164">
         <f>+'5'!P35</f>
-        <v>5700.0051747000007</v>
+        <v>5504.8752992999989</v>
       </c>
     </row>
     <row r="19" spans="1:21 16384:16384" ht="29.25" customHeight="1" x14ac:dyDescent="0.6">
@@ -23777,15 +23780,15 @@
       </c>
       <c r="N19" s="101">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>1061.1251199999999</v>
+        <v>1021.02784</v>
       </c>
       <c r="O19" s="101">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>53.155046400000003</v>
+        <v>52.954560000000001</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="0"/>
-        <v>5792.2961664000004</v>
+        <v>5751.9984000000004</v>
       </c>
       <c r="T19" s="163" t="str">
         <f>+'6'!A5</f>
@@ -23847,15 +23850,15 @@
       </c>
       <c r="N20" s="101">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>1221.2236800000001</v>
+        <v>1188.6809599999999</v>
       </c>
       <c r="O20" s="101">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>49.492537599999999</v>
+        <v>49.329824000000002</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="0"/>
-        <v>6558.9082176000002</v>
+        <v>6526.2027840000001</v>
       </c>
       <c r="T20" s="163" t="str">
         <f>+'7'!A5</f>
@@ -23917,15 +23920,15 @@
       </c>
       <c r="N21" s="101">
         <f>+'1'!N21+'2'!N21+'4'!N21+'3'!N21+'5'!N21+'6'!N21+'7'!N21+'8'!N21+'9'!N21+'10'!N21</f>
-        <v>1304.32384</v>
+        <v>1264.2265599999998</v>
       </c>
       <c r="O21" s="101">
         <f>+'1'!O21+'2'!O21+'4'!O21+'3'!O21+'5'!O21+'6'!O21+'7'!O21+'8'!O21+'9'!O21+'10'!O21</f>
-        <v>60.763359999999999</v>
+        <v>60.562873599999996</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="0"/>
-        <v>7321.5672000000004</v>
+        <v>7281.2694336000004</v>
       </c>
       <c r="T21" s="163" t="str">
         <f>+'8'!A5</f>
@@ -24188,15 +24191,15 @@
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>4385.7814400000007</v>
+        <v>4191.6223600000003</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>186.29298800000001</v>
+        <v>185.32219259999999</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>24272.062428000001</v>
+        <v>24076.932552600003</v>
       </c>
       <c r="T25" s="163" t="str">
         <f>+'12'!A5</f>
@@ -24326,7 +24329,7 @@
       </c>
       <c r="U30" s="165">
         <f>SUM(U14:U28)</f>
-        <v>24272.062427999997</v>
+        <v>24076.932552599996</v>
       </c>
     </row>
     <row r="31" spans="1:21 16384:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24448,7 +24451,7 @@
       </c>
       <c r="P36" s="153">
         <f>N25</f>
-        <v>4385.7814400000007</v>
+        <v>4191.6223600000003</v>
       </c>
     </row>
     <row r="37" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24470,7 +24473,7 @@
       <c r="O37" s="242"/>
       <c r="P37" s="153">
         <f>P35+P36</f>
-        <v>24085.769439999996</v>
+        <v>23891.610359999999</v>
       </c>
     </row>
     <row r="38" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24495,7 +24498,7 @@
       </c>
       <c r="P38" s="153">
         <f>O38*P37</f>
-        <v>602.14423599999998</v>
+        <v>597.29025899999999</v>
       </c>
     </row>
     <row r="39" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24505,7 +24508,7 @@
       <c r="O39" s="220"/>
       <c r="P39" s="160">
         <f>P37+P38</f>
-        <v>24687.913675999996</v>
+        <v>24488.900619</v>
       </c>
     </row>
     <row r="40" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24677,7 +24680,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -24705,7 +24708,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -25898,7 +25901,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -25926,7 +25929,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -27119,7 +27122,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -27147,7 +27150,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -28355,7 +28358,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -28383,7 +28386,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -29584,7 +29587,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -29612,7 +29615,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
@@ -29737,6 +29740,9 @@
       </c>
       <c r="F11" s="70"/>
       <c r="G11" s="71"/>
+      <c r="I11" t="s">
+        <v>124</v>
+      </c>
       <c r="K11" s="201" t="s">
         <v>59</v>
       </c>
@@ -29755,11 +29761,11 @@
         <v>60</v>
       </c>
       <c r="B12" s="76" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C12" s="77" t="str">
         <f>IF($O32&gt;21.99%,"No","Yes")</f>
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="F12" s="70"/>
       <c r="G12" s="71"/>
@@ -29780,7 +29786,7 @@
     <row r="13" spans="1:19 16383:16384" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="243"/>
       <c r="B13" s="64">
-        <v>0</v>
+        <v>3277876176746</v>
       </c>
       <c r="J13" s="78"/>
       <c r="K13" s="78"/>
@@ -29868,7 +29874,7 @@
       <c r="M15" s="250"/>
       <c r="N15" s="92">
         <f>IF(B12="Registered",18%,22%)</f>
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="O15" s="93">
         <f>IF(B11="Filer",0.5%,2.5%)</f>
@@ -29928,15 +29934,15 @@
       </c>
       <c r="N16" s="106">
         <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>159.27615</v>
+        <v>130.31684999999999</v>
       </c>
       <c r="O16" s="107">
         <f>(N16+M16)*$O$15</f>
-        <v>4.4162932499999998</v>
+        <v>4.2714967499999998</v>
       </c>
       <c r="P16" s="105">
         <f t="shared" ref="P16:P24" si="1">M16+N16+O16</f>
-        <v>887.67494324999996</v>
+        <v>858.57084674999999</v>
       </c>
       <c r="Q16" s="108"/>
       <c r="XFD16" t="s">
@@ -29992,15 +29998,15 @@
       </c>
       <c r="N17" s="118">
         <f t="shared" si="0"/>
-        <v>129.26760000000002</v>
+        <v>105.76439999999999</v>
       </c>
       <c r="O17" s="119">
         <f t="shared" ref="O17:O24" si="6">(N17+M17)*$O$15</f>
-        <v>3.0596130000000001</v>
+        <v>2.942097</v>
       </c>
       <c r="P17" s="120">
         <f t="shared" si="1"/>
-        <v>614.982213</v>
+        <v>591.36149699999999</v>
       </c>
       <c r="S17" s="64"/>
       <c r="XFD17" t="s">
@@ -30054,15 +30060,15 @@
       </c>
       <c r="N18" s="118">
         <f t="shared" si="0"/>
-        <v>159.27615</v>
+        <v>130.31684999999999</v>
       </c>
       <c r="O18" s="119">
         <f t="shared" si="6"/>
-        <v>4.4162932499999998</v>
+        <v>4.2714967499999998</v>
       </c>
       <c r="P18" s="120">
         <f t="shared" si="1"/>
-        <v>887.67494324999996</v>
+        <v>858.57084674999999</v>
       </c>
     </row>
     <row r="19" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30112,15 +30118,15 @@
       </c>
       <c r="N19" s="118">
         <f t="shared" si="0"/>
-        <v>220.53503999999998</v>
+        <v>180.43775999999997</v>
       </c>
       <c r="O19" s="119">
         <f t="shared" si="6"/>
-        <v>6.1148351999999999</v>
+        <v>5.9143487999999991</v>
       </c>
       <c r="P19" s="120">
         <f t="shared" si="1"/>
-        <v>1229.0818752</v>
+        <v>1188.7841087999998</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30172,15 +30178,15 @@
       </c>
       <c r="N20" s="118">
         <f t="shared" si="0"/>
-        <v>178.98496</v>
+        <v>146.44224</v>
       </c>
       <c r="O20" s="119">
         <f t="shared" si="6"/>
-        <v>4.2363648000000005</v>
+        <v>4.0736511999999996</v>
       </c>
       <c r="P20" s="120">
         <f t="shared" si="1"/>
-        <v>851.50932480000006</v>
+        <v>818.80389119999995</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30230,15 +30236,15 @@
       </c>
       <c r="N21" s="118">
         <f t="shared" si="0"/>
-        <v>220.53503999999998</v>
+        <v>180.43775999999997</v>
       </c>
       <c r="O21" s="119">
         <f t="shared" si="6"/>
-        <v>6.1148351999999999</v>
+        <v>5.9143487999999991</v>
       </c>
       <c r="P21" s="120">
         <f t="shared" si="1"/>
-        <v>1229.0818752</v>
+        <v>1188.7841087999998</v>
       </c>
     </row>
     <row r="22" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30445,15 +30451,15 @@
       </c>
       <c r="N25" s="142">
         <f>SUM(N16:N24)</f>
-        <v>1067.8749400000002</v>
+        <v>873.71585999999979</v>
       </c>
       <c r="O25" s="143">
         <f>SUM(O16:O24)</f>
-        <v>28.358234699999997</v>
+        <v>27.387439299999997</v>
       </c>
       <c r="P25" s="144">
         <f>SUM(P16:P24)</f>
-        <v>5700.0051746999998</v>
+        <v>5504.8752992999998</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -30588,11 +30594,11 @@
       </c>
       <c r="O32" s="156">
         <f>IF(B12="Registered",18%,22%)</f>
-        <v>0.22</v>
+        <v>0.18</v>
       </c>
       <c r="P32" s="153">
         <f>N25</f>
-        <v>1067.8749400000002</v>
+        <v>873.71585999999979</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -30614,7 +30620,7 @@
       <c r="O33" s="242"/>
       <c r="P33" s="153">
         <f>P31+P32</f>
-        <v>5671.6469400000005</v>
+        <v>5477.4878599999993</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -30639,7 +30645,7 @@
       </c>
       <c r="P34" s="153">
         <f>O34*P33</f>
-        <v>28.358234700000004</v>
+        <v>27.387439299999997</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -30649,7 +30655,7 @@
       <c r="O35" s="220"/>
       <c r="P35" s="160">
         <f>P33+P34</f>
-        <v>5700.0051747000007</v>
+        <v>5504.8752992999989</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -30821,7 +30827,7 @@
       <c r="M4" s="201"/>
       <c r="N4" s="202">
         <f ca="1">TODAY()</f>
-        <v>46189</v>
+        <v>46195</v>
       </c>
       <c r="O4" s="202"/>
       <c r="P4" s="202"/>
@@ -30849,7 +30855,7 @@
       <c r="M5" s="201"/>
       <c r="N5" s="202">
         <f ca="1">N4-1</f>
-        <v>46188</v>
+        <v>46194</v>
       </c>
       <c r="O5" s="200"/>
       <c r="P5" s="200"/>
